--- a/extenbooks/S1004_extenbook.xlsx
+++ b/extenbooks/S1004_extenbook.xlsx
@@ -15651,7 +15651,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -16500,14 +16500,42 @@
           <t>S1004-D-HP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S1002_components</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S1002 panel (book+ext) for S1004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Internal (S1002 panel)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>internal_computed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16690,11 +16718,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16717,88 +16745,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Real Interest Rate HP-filtered</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ingested</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1004_research.json", "adequacy_report": "Technical/docs/chapters/CH10_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1004_DPR.md", "epr": "Technical/docs/series/S1004_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1004_load.py", "processor": "Technical/code/P02_processors/P02_S1004_construct.py", "validator": "Technical/code/V03_validators/V03_S1004_validate.py", "processed": "Technical/data/processed/S1004.parquet", "chopped_csv": "Technical/chopped/S1004.csv", "extenbook_xlsx": "Technical/extenbooks/S1004_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S1004-A", "S1004-B", "S1004-C", "S1004-D"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["HP_filter_lambda_3", "HP_filter_lambda_6.25", "S1002_components"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1004_extenbook.xlsx
+++ b/extenbooks/S1004_extenbook.xlsx
@@ -15598,7 +15598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A119"/>
+  <dimension ref="A1:A129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15725,7 +15725,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shaikh's Figure 10.4 shows the real interest rate fluctuating around a slow-moving trend — the empirical hook for the next chapter's argument about the real-interest-rate floor.</t>
+          <t>Shaikh's Figure 10.8 shows the real interest rate fluctuating around a slow-moving trend — the empirical hook for the next chapter's argument about the real-interest-rate floor.</t>
         </is>
       </c>
     </row>
@@ -15766,7 +15766,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>| **S1004-B** | 1857–2011 | HP filter λ=3 on S1004-A | Percent | Computed in P02 |</t>
+          <t>| **S1004-B** | 1857–2011 | HP filter λ=100 on S1004-A (book `iblongrealHP3` column ≡ λ=100, see §7.4) | Percent | Computed in P02 |</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| **S1004-D** | 2012–present | Recomputed end-to-end (AAA − π_PPIACO), HP filtered λ=3 on full extended panel | Percent | Computed in P02 from FRED extensions |</t>
+          <t>| **S1004-D** | 2012–present | Recomputed end-to-end (AAA − π_PPIACO), HP filtered λ=100 on full extended panel | Percent | Computed in P02 from FRED extensions |</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HP filter: two-sided, default padding, λ ∈ {3, 6.25}, applied end-to-end on the</t>
+          <t>HP filter: two-sided, default padding, λ ∈ {100, 6.25}, applied end-to-end on the</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.4, p. 465</t>
+          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.8, Appendix 10.1</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">  iblongrealHP3[t]    = HP(iblongreal, λ=3)        # book replication</t>
+          <t xml:space="preserve">  iblongrealHP3[t]    = HP(iblongreal, λ=100)      # book replication (book 'HP3' column ≡ λ=100, see DPR §7.4)</t>
         </is>
       </c>
     </row>
@@ -16247,6 +16247,68 @@
       <c r="A119" t="inlineStr">
         <is>
           <t>Informational only; CD2's S054 likely used a single λ (=3) and a slightly different padding convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>- **CD2 / CD3** — the predecessor builds of this dataset (earlier reconstructions; a "CD2 divergence" note reports how the earlier build differed, for information only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: Phase 5 is ingestion (building the book-period series); Phase 6 is extension (carrying the series forward with live data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>- **IROP / ROP** — incremental / average rate of profit (the return on newly added capital, or on the whole capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>- **FRED** — the Federal Reserve Bank of St. Louis public economic-data service (source of the modern extension inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>- **BEA / NIPA** — the U.S. Bureau of Economic Analysis and its National Income and Product Accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>- **No-Lazy-Splices rule** — an internal quality rule: a derived (formula) quantity is never extended by splicing onto the published rate; the formula is recomputed from extended components so it stays analytically consistent across the book/extension boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
         </is>
       </c>
     </row>
@@ -16265,8 +16327,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -16373,12 +16435,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HP_filter_lambda_3</t>
+          <t>HP_filter_lambda_100_book_match</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HP trend of iblongreal, lambda=3</t>
+          <t>HP trend of the real long rate, lambda=100 fitted over the BOOK period to match Shaikh's published Fig 10.x</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16502,17 +16564,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S1002_components</t>
+          <t>HP_filter_lambda_100_full_panel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S1002 panel (book+ext) for S1004</t>
+          <t>HP trend of the real long rate, lambda=100 refitted over the FULL extended panel (book + extension years)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Internal (S1002 panel)</t>
+          <t>Internal (HP filter)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -16703,7 +16765,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:26:07.337459+00:00</t>
+          <t>2026-07-02T06:18:17.904325+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1004_extenbook.xlsx
+++ b/extenbooks/S1004_extenbook.xlsx
@@ -15651,7 +15651,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:17.904325+00:00</t>
+          <t>2026-07-11T03:44:22.184728+00:00</t>
         </is>
       </c>
     </row>
@@ -16780,11 +16780,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16807,6 +16807,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>USLR_iblongreal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Formula series reconstructing Figure 10.8 (real interest rate, HP-filtered); HP trend recomputed end-to-end. Fixed figure reference (was 10.2/10.4, correct is 10.8). lambda documented (book HP3 column matches lambda=100).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1004_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1004_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-26 PB-fix: units label corrected percent-&gt;rate_decimal (values are decimals; matches chopped col + S1007 convention; viz formats as %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
